--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.4616819157649</v>
+        <v>8.850023311311796</v>
       </c>
       <c r="D2" t="n">
-        <v>54.79873429807461</v>
+        <v>8.904794323437125</v>
       </c>
       <c r="E2" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F2" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.74991541086809</v>
+        <v>8.571861254266064</v>
       </c>
       <c r="D3" t="n">
-        <v>53.05527084296873</v>
+        <v>8.621481511982418</v>
       </c>
       <c r="E3" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F3" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.58135948423925</v>
+        <v>7.081970916188879</v>
       </c>
       <c r="D4" t="n">
-        <v>43.87093039272487</v>
+        <v>7.129026188817791</v>
       </c>
       <c r="E4" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F4" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>78.88997994247194</v>
+        <v>12.81962174065169</v>
       </c>
       <c r="D5" t="n">
-        <v>78.83890144840372</v>
+        <v>12.8113214853656</v>
       </c>
       <c r="E5" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F5" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.71296107805085</v>
+        <v>7.753356175183263</v>
       </c>
       <c r="D6" t="n">
-        <v>47.6059427314318</v>
+        <v>7.735965693857667</v>
       </c>
       <c r="E6" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F6" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>80.27239082326552</v>
+        <v>13.04426350878065</v>
       </c>
       <c r="D7" t="n">
-        <v>80.06124871356462</v>
+        <v>13.00995291595425</v>
       </c>
       <c r="E7" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F7" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.98363388584398</v>
+        <v>4.222340506449648</v>
       </c>
       <c r="D8" t="n">
-        <v>25.58674860840745</v>
+        <v>4.157846648866212</v>
       </c>
       <c r="E8" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F8" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>87.20884446600014</v>
+        <v>14.17143722572502</v>
       </c>
       <c r="D9" t="n">
-        <v>86.98975967215478</v>
+        <v>14.13583594672515</v>
       </c>
       <c r="E9" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F9" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.65356650500797</v>
+        <v>6.118704557063796</v>
       </c>
       <c r="D10" t="n">
-        <v>37.2692177039235</v>
+        <v>6.05624787688757</v>
       </c>
       <c r="E10" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F10" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.39339489287207</v>
+        <v>8.351426670091712</v>
       </c>
       <c r="D11" t="n">
-        <v>51.16888292418992</v>
+        <v>8.314943475180863</v>
       </c>
       <c r="E11" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F11" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>64.57869565784607</v>
+        <v>10.49403804439999</v>
       </c>
       <c r="D12" t="n">
-        <v>64.35038552507652</v>
+        <v>10.45693764782493</v>
       </c>
       <c r="E12" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F12" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>71.72628976730915</v>
+        <v>11.65552208718774</v>
       </c>
       <c r="D13" t="n">
-        <v>71.35872628391121</v>
+        <v>11.59579302113557</v>
       </c>
       <c r="E13" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F13" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>68.48217795860118</v>
+        <v>11.12835391827269</v>
       </c>
       <c r="D14" t="n">
-        <v>68.08460118759875</v>
+        <v>11.0637476929848</v>
       </c>
       <c r="E14" t="n">
-        <v>17.44188325500328</v>
+        <v>2.834306028938033</v>
       </c>
       <c r="F14" t="n">
-        <v>17.420092930189</v>
+        <v>2.830765101155713</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
